--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/104.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/104.xlsx
@@ -426,13 +426,13 @@
         <v>-9.247929071434717</v>
       </c>
       <c r="E2">
-        <v>-16.15032007834511</v>
+        <v>-18.33083918320049</v>
       </c>
       <c r="F2">
-        <v>-0.09820558795159755</v>
+        <v>-1.262838797508729</v>
       </c>
       <c r="G2">
-        <v>-15.40062064023971</v>
+        <v>-12.39074461948562</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.646461984002661</v>
       </c>
       <c r="E3">
-        <v>-17.47613952746679</v>
+        <v>-17.44463946226944</v>
       </c>
       <c r="F3">
-        <v>-0.1206965913050069</v>
+        <v>-0.3272500031930636</v>
       </c>
       <c r="G3">
-        <v>-15.81369034113665</v>
+        <v>-12.34388221317363</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.936653496031578</v>
       </c>
       <c r="E4">
-        <v>-17.87318254303731</v>
+        <v>-17.95521132121225</v>
       </c>
       <c r="F4">
-        <v>-0.3565501865974849</v>
+        <v>-0.5955060178134471</v>
       </c>
       <c r="G4">
-        <v>-15.13237421531199</v>
+        <v>-11.64546436058114</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.09755841175967</v>
       </c>
       <c r="E5">
-        <v>-18.95566444135682</v>
+        <v>-16.95286077045846</v>
       </c>
       <c r="F5">
-        <v>0.02882621000251225</v>
+        <v>-0.5460027818221487</v>
       </c>
       <c r="G5">
-        <v>-15.2393568036469</v>
+        <v>-12.43439799111247</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.18063407049195</v>
       </c>
       <c r="E6">
-        <v>-18.30495895424665</v>
+        <v>-19.58866812357101</v>
       </c>
       <c r="F6">
-        <v>-0.09602863841704044</v>
+        <v>-0.7196807765953014</v>
       </c>
       <c r="G6">
-        <v>-16.3633950296012</v>
+        <v>-12.63781404046869</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.20865640119034</v>
       </c>
       <c r="E7">
-        <v>-20.02570662157726</v>
+        <v>-18.36081768113127</v>
       </c>
       <c r="F7">
-        <v>0.008498902305215175</v>
+        <v>0.03603963334609034</v>
       </c>
       <c r="G7">
-        <v>-15.6547676561265</v>
+        <v>-11.81424383515586</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.21487401447593</v>
       </c>
       <c r="E8">
-        <v>-19.06095146203516</v>
+        <v>-18.33400005805784</v>
       </c>
       <c r="F8">
-        <v>0.2397268940204608</v>
+        <v>-0.4695535825851851</v>
       </c>
       <c r="G8">
-        <v>-14.89394589130572</v>
+        <v>-12.25805201962167</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.22280688663542</v>
       </c>
       <c r="E9">
-        <v>-20.48766531204774</v>
+        <v>-21.03114559160428</v>
       </c>
       <c r="F9">
-        <v>-0.215760862817681</v>
+        <v>-0.424188870138273</v>
       </c>
       <c r="G9">
-        <v>-14.74575444140574</v>
+        <v>-12.6650547418552</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.24028924633927</v>
       </c>
       <c r="E10">
-        <v>-21.19547032792062</v>
+        <v>-21.40937279767293</v>
       </c>
       <c r="F10">
-        <v>0.03270711128462793</v>
+        <v>0.6499079241298864</v>
       </c>
       <c r="G10">
-        <v>-14.59722338507435</v>
+        <v>-12.42340918010989</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.27040386586567</v>
       </c>
       <c r="E11">
-        <v>-21.33376539564086</v>
+        <v>-20.98465627744154</v>
       </c>
       <c r="F11">
-        <v>0.6125112777305027</v>
+        <v>0.3332346631832745</v>
       </c>
       <c r="G11">
-        <v>-14.60172029922157</v>
+        <v>-12.11137485347138</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.3118630334423</v>
       </c>
       <c r="E12">
-        <v>-22.34141426098363</v>
+        <v>-22.15573324124712</v>
       </c>
       <c r="F12">
-        <v>0.3290505794317343</v>
+        <v>0.850578270723261</v>
       </c>
       <c r="G12">
-        <v>-13.41021687678353</v>
+        <v>-11.01285468758488</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.34621621391575</v>
       </c>
       <c r="E13">
-        <v>-22.98381452676373</v>
+        <v>-23.85000292105488</v>
       </c>
       <c r="F13">
-        <v>0.8271205626107846</v>
+        <v>0.35968360598726</v>
       </c>
       <c r="G13">
-        <v>-14.09830872512845</v>
+        <v>-11.62413313922319</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.36063259937223</v>
       </c>
       <c r="E14">
-        <v>-24.66820307628675</v>
+        <v>-23.01158765785277</v>
       </c>
       <c r="F14">
-        <v>0.9499475676282841</v>
+        <v>1.014928020173488</v>
       </c>
       <c r="G14">
-        <v>-13.3916353190924</v>
+        <v>-11.27500460285516</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.33685440042635</v>
       </c>
       <c r="E15">
-        <v>-24.11955580788745</v>
+        <v>-25.94223942513073</v>
       </c>
       <c r="F15">
-        <v>1.414830667548978</v>
+        <v>1.278456542026095</v>
       </c>
       <c r="G15">
-        <v>-14.09764263715188</v>
+        <v>-11.40204365797218</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.24678281219557</v>
       </c>
       <c r="E16">
-        <v>-25.79010534084304</v>
+        <v>-23.5584824068111</v>
       </c>
       <c r="F16">
-        <v>1.689860242422053</v>
+        <v>1.299712449581931</v>
       </c>
       <c r="G16">
-        <v>-13.03173125112314</v>
+        <v>-11.20714565978428</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.07388098447183</v>
       </c>
       <c r="E17">
-        <v>-26.13744382570536</v>
+        <v>-23.28304703224257</v>
       </c>
       <c r="F17">
-        <v>1.448508772677195</v>
+        <v>2.562729198834754</v>
       </c>
       <c r="G17">
-        <v>-13.52470525943568</v>
+        <v>-11.08968120917772</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.799017985516731</v>
       </c>
       <c r="E18">
-        <v>-27.22665503640028</v>
+        <v>-25.98305908983587</v>
       </c>
       <c r="F18">
-        <v>2.44846419929259</v>
+        <v>2.073281691951443</v>
       </c>
       <c r="G18">
-        <v>-12.3438034638562</v>
+        <v>-9.728354883709057</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.403902284769892</v>
       </c>
       <c r="E19">
-        <v>-27.48170322098628</v>
+        <v>-26.58354380020097</v>
       </c>
       <c r="F19">
-        <v>2.321112651520999</v>
+        <v>2.058081150110072</v>
       </c>
       <c r="G19">
-        <v>-11.74702801151063</v>
+        <v>-10.17998550037259</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.891252530430481</v>
       </c>
       <c r="E20">
-        <v>-28.62692259820806</v>
+        <v>-26.10213531386756</v>
       </c>
       <c r="F20">
-        <v>3.025746815364343</v>
+        <v>2.549351065279541</v>
       </c>
       <c r="G20">
-        <v>-11.5775463555222</v>
+        <v>-8.764043242046968</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.266218595389143</v>
       </c>
       <c r="E21">
-        <v>-28.91634642898629</v>
+        <v>-28.54047402940163</v>
       </c>
       <c r="F21">
-        <v>2.790689281145955</v>
+        <v>3.344583771967067</v>
       </c>
       <c r="G21">
-        <v>-12.86941578302053</v>
+        <v>-8.966264926755546</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.540409567505789</v>
       </c>
       <c r="E22">
-        <v>-30.25421388320537</v>
+        <v>-28.837066434534</v>
       </c>
       <c r="F22">
-        <v>3.07434713088659</v>
+        <v>2.249846547123352</v>
       </c>
       <c r="G22">
-        <v>-11.06609578860843</v>
+        <v>-8.194455991542959</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.74601118019758</v>
       </c>
       <c r="E23">
-        <v>-29.61252232360747</v>
+        <v>-30.16445499989934</v>
       </c>
       <c r="F23">
-        <v>3.15863351412144</v>
+        <v>3.049593856156135</v>
       </c>
       <c r="G23">
-        <v>-11.04615580519168</v>
+        <v>-9.29301225086661</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.91163592726105</v>
       </c>
       <c r="E24">
-        <v>-31.41663240470828</v>
+        <v>-28.57435154345301</v>
       </c>
       <c r="F24">
-        <v>3.436169728755386</v>
+        <v>3.565691599122311</v>
       </c>
       <c r="G24">
-        <v>-11.14335215022555</v>
+        <v>-7.34886878956626</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.067230686133572</v>
       </c>
       <c r="E25">
-        <v>-30.03003630592966</v>
+        <v>-31.95413962704872</v>
       </c>
       <c r="F25">
-        <v>3.261182085118407</v>
+        <v>3.153636801947753</v>
       </c>
       <c r="G25">
-        <v>-11.02167461113667</v>
+        <v>-7.373989821825369</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.253177309814725</v>
       </c>
       <c r="E26">
-        <v>-32.15715338104958</v>
+        <v>-30.98380991600317</v>
       </c>
       <c r="F26">
-        <v>3.045402317097969</v>
+        <v>4.042102259820362</v>
       </c>
       <c r="G26">
-        <v>-10.4315501948921</v>
+        <v>-7.387482204877805</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.496146703239353</v>
       </c>
       <c r="E27">
-        <v>-31.66127415602466</v>
+        <v>-31.16933923186042</v>
       </c>
       <c r="F27">
-        <v>3.233680287345464</v>
+        <v>3.575086942204863</v>
       </c>
       <c r="G27">
-        <v>-10.6124669080152</v>
+        <v>-7.784864385499036</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.815999380841329</v>
       </c>
       <c r="E28">
-        <v>-31.12844258309715</v>
+        <v>-32.76382172267216</v>
       </c>
       <c r="F28">
-        <v>3.027844241628231</v>
+        <v>3.31415452379263</v>
       </c>
       <c r="G28">
-        <v>-10.61620750059297</v>
+        <v>-7.21898163413564</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.234696220558771</v>
       </c>
       <c r="E29">
-        <v>-31.36969477161878</v>
+        <v>-30.25540034339538</v>
       </c>
       <c r="F29">
-        <v>2.997413336718989</v>
+        <v>3.35550331107077</v>
       </c>
       <c r="G29">
-        <v>-9.469302441590896</v>
+        <v>-7.639381583996376</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.756540019647275</v>
       </c>
       <c r="E30">
-        <v>-29.95504251212564</v>
+        <v>-30.29562451376852</v>
       </c>
       <c r="F30">
-        <v>2.624971068746303</v>
+        <v>3.318258255906099</v>
       </c>
       <c r="G30">
-        <v>-9.532538143484516</v>
+        <v>-6.911924920602804</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.378191940661572</v>
       </c>
       <c r="E31">
-        <v>-31.18811428509622</v>
+        <v>-30.04345643865139</v>
       </c>
       <c r="F31">
-        <v>2.989209185961662</v>
+        <v>3.463691407345997</v>
       </c>
       <c r="G31">
-        <v>-9.583173954589865</v>
+        <v>-7.904356631029334</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.097052142326312</v>
       </c>
       <c r="E32">
-        <v>-30.72434194078568</v>
+        <v>-30.05080388772884</v>
       </c>
       <c r="F32">
-        <v>2.610921957594823</v>
+        <v>2.979474212243963</v>
       </c>
       <c r="G32">
-        <v>-9.079535976209137</v>
+        <v>-6.871178711277619</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8977360760119434</v>
       </c>
       <c r="E33">
-        <v>-29.99438815854128</v>
+        <v>-28.7885936487559</v>
       </c>
       <c r="F33">
-        <v>2.76600393254253</v>
+        <v>2.706911515496425</v>
       </c>
       <c r="G33">
-        <v>-9.296395190294398</v>
+        <v>-6.957704523800177</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7638819010243671</v>
       </c>
       <c r="E34">
-        <v>-30.44853749558552</v>
+        <v>-28.46370280954959</v>
       </c>
       <c r="F34">
-        <v>2.290418325777666</v>
+        <v>2.579278322807882</v>
       </c>
       <c r="G34">
-        <v>-9.15019052004866</v>
+        <v>-8.011321172645673</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.6843350881253133</v>
       </c>
       <c r="E35">
-        <v>-29.08438451398891</v>
+        <v>-28.33954110920729</v>
       </c>
       <c r="F35">
-        <v>2.6024229080421</v>
+        <v>2.781305535207042</v>
       </c>
       <c r="G35">
-        <v>-9.516978590849629</v>
+        <v>-7.350657055316157</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6439767560889098</v>
       </c>
       <c r="E36">
-        <v>-28.30843954972261</v>
+        <v>-26.84777120160052</v>
       </c>
       <c r="F36">
-        <v>2.272543813960059</v>
+        <v>2.445112624780863</v>
       </c>
       <c r="G36">
-        <v>-9.357783564450049</v>
+        <v>-7.669237418965763</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6302956045383792</v>
       </c>
       <c r="E37">
-        <v>-28.98710836383014</v>
+        <v>-29.90459531168019</v>
       </c>
       <c r="F37">
-        <v>2.250113281427054</v>
+        <v>2.859937482550383</v>
       </c>
       <c r="G37">
-        <v>-8.601425901560889</v>
+        <v>-6.600071061150059</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.6361184296968548</v>
       </c>
       <c r="E38">
-        <v>-27.58649210952377</v>
+        <v>-26.03522258193022</v>
       </c>
       <c r="F38">
-        <v>2.007462931594606</v>
+        <v>2.498206005095895</v>
       </c>
       <c r="G38">
-        <v>-8.738535025643845</v>
+        <v>-6.260182444693419</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.6553437489761395</v>
       </c>
       <c r="E39">
-        <v>-27.03445754256673</v>
+        <v>-27.59558981380518</v>
       </c>
       <c r="F39">
-        <v>2.160097909234443</v>
+        <v>2.721119673189242</v>
       </c>
       <c r="G39">
-        <v>-8.868668272691423</v>
+        <v>-8.283337721145198</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.6854507214264878</v>
       </c>
       <c r="E40">
-        <v>-27.30952158226664</v>
+        <v>-27.15102499199817</v>
       </c>
       <c r="F40">
-        <v>1.783180800551834</v>
+        <v>2.814687084805057</v>
       </c>
       <c r="G40">
-        <v>-9.106839020805277</v>
+        <v>-7.892846105798802</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7280161860769443</v>
       </c>
       <c r="E41">
-        <v>-27.6724697170334</v>
+        <v>-25.12503100570653</v>
       </c>
       <c r="F41">
-        <v>2.327582200936864</v>
+        <v>2.259742224117195</v>
       </c>
       <c r="G41">
-        <v>-9.591514819793975</v>
+        <v>-7.75694775247128</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.7876637003940876</v>
       </c>
       <c r="E42">
-        <v>-26.95971055059612</v>
+        <v>-24.46659541346527</v>
       </c>
       <c r="F42">
-        <v>2.125366120769865</v>
+        <v>2.305241132083361</v>
       </c>
       <c r="G42">
-        <v>-9.571860302652901</v>
+        <v>-6.828027366549362</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8692409523911946</v>
       </c>
       <c r="E43">
-        <v>-24.76897520837944</v>
+        <v>-26.09706795145297</v>
       </c>
       <c r="F43">
-        <v>1.948219751681191</v>
+        <v>2.223060458786427</v>
       </c>
       <c r="G43">
-        <v>-9.897173732942488</v>
+        <v>-7.058854740813179</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.9783869564351395</v>
       </c>
       <c r="E44">
-        <v>-25.15010969476101</v>
+        <v>-24.61378440413658</v>
       </c>
       <c r="F44">
-        <v>2.219243341794327</v>
+        <v>2.143528904443647</v>
       </c>
       <c r="G44">
-        <v>-9.657362374048912</v>
+        <v>-8.64035431414214</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.122310952405285</v>
       </c>
       <c r="E45">
-        <v>-24.44246317547839</v>
+        <v>-23.83199770840038</v>
       </c>
       <c r="F45">
-        <v>1.661036370274241</v>
+        <v>2.133528853157051</v>
       </c>
       <c r="G45">
-        <v>-9.40729391656051</v>
+        <v>-7.213364182825871</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.30424989241401</v>
       </c>
       <c r="E46">
-        <v>-23.59126403015263</v>
+        <v>-21.61729768173511</v>
       </c>
       <c r="F46">
-        <v>1.980580752638956</v>
+        <v>2.587056692720169</v>
       </c>
       <c r="G46">
-        <v>-9.404642689540479</v>
+        <v>-7.379512117709914</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.526313802328103</v>
       </c>
       <c r="E47">
-        <v>-23.1871882944482</v>
+        <v>-22.51208791785871</v>
       </c>
       <c r="F47">
-        <v>1.703510080485383</v>
+        <v>2.514943996836861</v>
       </c>
       <c r="G47">
-        <v>-8.476808387954737</v>
+        <v>-7.078335353211602</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.791864877727219</v>
       </c>
       <c r="E48">
-        <v>-22.68237665444315</v>
+        <v>-22.40302867833199</v>
       </c>
       <c r="F48">
-        <v>2.390703797030186</v>
+        <v>2.895237531053281</v>
       </c>
       <c r="G48">
-        <v>-9.06096098096112</v>
+        <v>-6.322962056790275</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.097870554464182</v>
       </c>
       <c r="E49">
-        <v>-23.20090504221744</v>
+        <v>-21.57434057729835</v>
       </c>
       <c r="F49">
-        <v>2.061402903395298</v>
+        <v>2.156058789778392</v>
       </c>
       <c r="G49">
-        <v>-8.80309634104748</v>
+        <v>-7.501101063816697</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.4404844013198</v>
       </c>
       <c r="E50">
-        <v>-21.82921667987206</v>
+        <v>-20.57008806746134</v>
       </c>
       <c r="F50">
-        <v>1.832008088742448</v>
+        <v>2.647023865743631</v>
       </c>
       <c r="G50">
-        <v>-9.386832218915814</v>
+        <v>-9.536711857308129</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.818142371533742</v>
       </c>
       <c r="E51">
-        <v>-20.75861296887467</v>
+        <v>-19.03760265005161</v>
       </c>
       <c r="F51">
-        <v>2.10643295541148</v>
+        <v>2.352530970374379</v>
       </c>
       <c r="G51">
-        <v>-9.638682379710993</v>
+        <v>-6.630990011904707</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.222924760021402</v>
       </c>
       <c r="E52">
-        <v>-21.03716846203449</v>
+        <v>-19.98850973607826</v>
       </c>
       <c r="F52">
-        <v>2.404550786535383</v>
+        <v>1.95092685635354</v>
       </c>
       <c r="G52">
-        <v>-9.931790620394629</v>
+        <v>-6.954892516923732</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.647676606349924</v>
       </c>
       <c r="E53">
-        <v>-19.59398908053002</v>
+        <v>-19.82823345552479</v>
       </c>
       <c r="F53">
-        <v>2.025696954865028</v>
+        <v>2.606609476895849</v>
       </c>
       <c r="G53">
-        <v>-9.022564126272499</v>
+        <v>-7.755950261117209</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.088145963853018</v>
       </c>
       <c r="E54">
-        <v>-20.05562172087194</v>
+        <v>-18.10913868120697</v>
       </c>
       <c r="F54">
-        <v>1.847617844080802</v>
+        <v>1.764113439674195</v>
       </c>
       <c r="G54">
-        <v>-9.858560317630943</v>
+        <v>-7.220743650113063</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.533442404088944</v>
       </c>
       <c r="E55">
-        <v>-18.29885909975832</v>
+        <v>-17.97756386891411</v>
       </c>
       <c r="F55">
-        <v>1.466996276372874</v>
+        <v>1.983072481786577</v>
       </c>
       <c r="G55">
-        <v>-9.891831904243711</v>
+        <v>-7.18424006026424</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.974766896967517</v>
       </c>
       <c r="E56">
-        <v>-18.35789228692231</v>
+        <v>-17.64365230948453</v>
       </c>
       <c r="F56">
-        <v>1.742161703500008</v>
+        <v>1.821762840704624</v>
       </c>
       <c r="G56">
-        <v>-10.26757114745885</v>
+        <v>-7.390553428257445</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.406085208628328</v>
       </c>
       <c r="E57">
-        <v>-17.70823287730791</v>
+        <v>-19.2142403071948</v>
       </c>
       <c r="F57">
-        <v>1.621167047177501</v>
+        <v>1.738934384098701</v>
       </c>
       <c r="G57">
-        <v>-10.48185460261994</v>
+        <v>-7.426909363136093</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.815581036956885</v>
       </c>
       <c r="E58">
-        <v>-17.40573081359553</v>
+        <v>-16.18144880867384</v>
       </c>
       <c r="F58">
-        <v>1.654682792294769</v>
+        <v>1.87101093953586</v>
       </c>
       <c r="G58">
-        <v>-9.585011438663155</v>
+        <v>-8.831108129500459</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.19519549848856</v>
       </c>
       <c r="E59">
-        <v>-17.20103020302681</v>
+        <v>-15.69136376614173</v>
       </c>
       <c r="F59">
-        <v>1.573310605582968</v>
+        <v>2.494301081159098</v>
       </c>
       <c r="G59">
-        <v>-9.832701010520958</v>
+        <v>-7.975211329383983</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.53916939647486</v>
       </c>
       <c r="E60">
-        <v>-16.1924665859345</v>
+        <v>-16.08821658580392</v>
       </c>
       <c r="F60">
-        <v>1.383525006662379</v>
+        <v>1.894877861145319</v>
       </c>
       <c r="G60">
-        <v>-9.765232532815656</v>
+        <v>-7.539189483678731</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.837397696204987</v>
       </c>
       <c r="E61">
-        <v>-16.06509872599476</v>
+        <v>-15.64498313535517</v>
       </c>
       <c r="F61">
-        <v>0.8143587344032555</v>
+        <v>1.652157928451036</v>
       </c>
       <c r="G61">
-        <v>-9.872049419461819</v>
+        <v>-6.916311913827782</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.084733697854267</v>
       </c>
       <c r="E62">
-        <v>-15.63197735800514</v>
+        <v>-15.51987951241927</v>
       </c>
       <c r="F62">
-        <v>1.373988841121351</v>
+        <v>1.778001847549532</v>
       </c>
       <c r="G62">
-        <v>-10.29964508820242</v>
+        <v>-7.599321149977116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.277416354233381</v>
       </c>
       <c r="E63">
-        <v>-14.7682207542561</v>
+        <v>-12.7491009915081</v>
       </c>
       <c r="F63">
-        <v>1.448023349379154</v>
+        <v>1.862389291607523</v>
       </c>
       <c r="G63">
-        <v>-9.797139131259696</v>
+        <v>-9.036259945061621</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.409720331585024</v>
       </c>
       <c r="E64">
-        <v>-15.38014891843859</v>
+        <v>-13.42997517245737</v>
       </c>
       <c r="F64">
-        <v>0.611721015228232</v>
+        <v>1.854945582125966</v>
       </c>
       <c r="G64">
-        <v>-10.02518731086266</v>
+        <v>-8.870167790944089</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.48171454873313</v>
       </c>
       <c r="E65">
-        <v>-14.98272098257742</v>
+        <v>-12.81987651177399</v>
       </c>
       <c r="F65">
-        <v>0.5198973169953096</v>
+        <v>1.229968884470629</v>
       </c>
       <c r="G65">
-        <v>-10.241829964325</v>
+        <v>-9.37562356606875</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.493379691139502</v>
       </c>
       <c r="E66">
-        <v>-14.91040578114894</v>
+        <v>-13.27850224537481</v>
       </c>
       <c r="F66">
-        <v>1.007689745807826</v>
+        <v>1.388250014327947</v>
       </c>
       <c r="G66">
-        <v>-10.26044105301017</v>
+        <v>-7.696724211969232</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.444842462087459</v>
       </c>
       <c r="E67">
-        <v>-14.87140203452087</v>
+        <v>-13.38414248702574</v>
       </c>
       <c r="F67">
-        <v>0.7350856306901483</v>
+        <v>1.177317852348692</v>
       </c>
       <c r="G67">
-        <v>-10.58628275997083</v>
+        <v>-9.65955751127218</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.340814709655271</v>
       </c>
       <c r="E68">
-        <v>-13.7959121000692</v>
+        <v>-12.72980969223543</v>
       </c>
       <c r="F68">
-        <v>0.6769408659528454</v>
+        <v>0.8934694781054138</v>
       </c>
       <c r="G68">
-        <v>-10.4775857333711</v>
+        <v>-8.654571847159215</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.183738189754521</v>
       </c>
       <c r="E69">
-        <v>-13.05734516026221</v>
+        <v>-11.92145896797024</v>
       </c>
       <c r="F69">
-        <v>0.1713410230823476</v>
+        <v>1.205386253425151</v>
       </c>
       <c r="G69">
-        <v>-9.703863845989362</v>
+        <v>-8.737544096732893</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.97822272406581</v>
       </c>
       <c r="E70">
-        <v>-14.8333402104864</v>
+        <v>-13.93195651620763</v>
       </c>
       <c r="F70">
-        <v>0.405486524790253</v>
+        <v>0.6937658362711062</v>
       </c>
       <c r="G70">
-        <v>-9.745935668824561</v>
+        <v>-7.929152822354058</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.731769042876632</v>
       </c>
       <c r="E71">
-        <v>-14.21240491150266</v>
+        <v>-13.27507871902501</v>
       </c>
       <c r="F71">
-        <v>-0.1337690572885859</v>
+        <v>0.495820818432942</v>
       </c>
       <c r="G71">
-        <v>-8.621188699013423</v>
+        <v>-8.728819328606329</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.447065107297244</v>
       </c>
       <c r="E72">
-        <v>-14.14302868970515</v>
+        <v>-14.76990534658696</v>
       </c>
       <c r="F72">
-        <v>-0.05489439829622539</v>
+        <v>0.1895228592063939</v>
       </c>
       <c r="G72">
-        <v>-9.087040129915588</v>
+        <v>-8.68620610421382</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.130110915417433</v>
       </c>
       <c r="E73">
-        <v>-14.28866894226583</v>
+        <v>-13.30387528523979</v>
       </c>
       <c r="F73">
-        <v>-0.3306686754644172</v>
+        <v>-0.1178710300940578</v>
       </c>
       <c r="G73">
-        <v>-9.045736112925297</v>
+        <v>-8.82382709886005</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.787427373848868</v>
       </c>
       <c r="E74">
-        <v>-13.88103835446539</v>
+        <v>-13.6814956757914</v>
       </c>
       <c r="F74">
-        <v>0.02429421194179615</v>
+        <v>-0.125344560802115</v>
       </c>
       <c r="G74">
-        <v>-7.709045198924946</v>
+        <v>-9.077619742818422</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.419882275615751</v>
       </c>
       <c r="E75">
-        <v>-13.95934472700602</v>
+        <v>-13.43889173777848</v>
       </c>
       <c r="F75">
-        <v>-0.4826691236737097</v>
+        <v>0.058388985873621</v>
       </c>
       <c r="G75">
-        <v>-8.234837985275046</v>
+        <v>-8.132303092763959</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.03381634133531</v>
       </c>
       <c r="E76">
-        <v>-14.725059868489</v>
+        <v>-13.27463492857226</v>
       </c>
       <c r="F76">
-        <v>-0.7297727766636078</v>
+        <v>-0.556487428039382</v>
       </c>
       <c r="G76">
-        <v>-7.894066720218915</v>
+        <v>-7.158170754974452</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.634525988303892</v>
       </c>
       <c r="E77">
-        <v>-15.63123015979387</v>
+        <v>-13.0215611586536</v>
       </c>
       <c r="F77">
-        <v>-0.4616774653193674</v>
+        <v>-0.03722614996191474</v>
       </c>
       <c r="G77">
-        <v>-8.271525323531197</v>
+        <v>-6.849975457560488</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.221420375801478</v>
       </c>
       <c r="E78">
-        <v>-14.9980543955674</v>
+        <v>-14.01706012823378</v>
       </c>
       <c r="F78">
-        <v>-0.5633719895240488</v>
+        <v>-0.1554524024242658</v>
       </c>
       <c r="G78">
-        <v>-7.782705341712921</v>
+        <v>-6.615092493449198</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.8012322915267</v>
       </c>
       <c r="E79">
-        <v>-15.55853003807473</v>
+        <v>-15.43663257473626</v>
       </c>
       <c r="F79">
-        <v>-1.034498494559642</v>
+        <v>-0.5992593505155317</v>
       </c>
       <c r="G79">
-        <v>-6.952598943053681</v>
+        <v>-6.587021643008148</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.378422179017949</v>
       </c>
       <c r="E80">
-        <v>-16.27814984263363</v>
+        <v>-15.98361789317475</v>
       </c>
       <c r="F80">
-        <v>-0.4541973076720879</v>
+        <v>-0.5103158857421431</v>
       </c>
       <c r="G80">
-        <v>-6.593633304450429</v>
+        <v>-7.385067225810054</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.952640584806796</v>
       </c>
       <c r="E81">
-        <v>-16.40772759788911</v>
+        <v>-14.51419147632183</v>
       </c>
       <c r="F81">
-        <v>-1.108149468709949</v>
+        <v>-0.4552137144753229</v>
       </c>
       <c r="G81">
-        <v>-6.136923356812878</v>
+        <v>-4.982783204272234</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.531499070877267</v>
       </c>
       <c r="E82">
-        <v>-16.82684692424702</v>
+        <v>-15.39237126978529</v>
       </c>
       <c r="F82">
-        <v>-1.240418205384557</v>
+        <v>-1.378086240790613</v>
       </c>
       <c r="G82">
-        <v>-6.856741336416063</v>
+        <v>-4.833152938718436</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.118965197597657</v>
       </c>
       <c r="E83">
-        <v>-17.75065109333776</v>
+        <v>-17.13875009999932</v>
       </c>
       <c r="F83">
-        <v>-1.027706710224089</v>
+        <v>-0.412471613225674</v>
       </c>
       <c r="G83">
-        <v>-6.777414523994928</v>
+        <v>-5.166863014978643</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.714977295590004</v>
       </c>
       <c r="E84">
-        <v>-19.10093788752289</v>
+        <v>-17.83335008566584</v>
       </c>
       <c r="F84">
-        <v>-0.9860216057804124</v>
+        <v>-0.2763236320037556</v>
       </c>
       <c r="G84">
-        <v>-5.170160642645884</v>
+        <v>-4.370881320537627</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.327459887071879</v>
       </c>
       <c r="E85">
-        <v>-19.10550258932262</v>
+        <v>-18.36689036477555</v>
       </c>
       <c r="F85">
-        <v>-0.8236326019726113</v>
+        <v>-0.5287545157610574</v>
       </c>
       <c r="G85">
-        <v>-5.765597356595198</v>
+        <v>-3.134431725178313</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.9604271736788227</v>
       </c>
       <c r="E86">
-        <v>-19.84492088224305</v>
+        <v>-19.92916408420774</v>
       </c>
       <c r="F86">
-        <v>-1.547585122016642</v>
+        <v>-0.8377496392511206</v>
       </c>
       <c r="G86">
-        <v>-5.138552635363753</v>
+        <v>-4.058915899551861</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6151461889876713</v>
       </c>
       <c r="E87">
-        <v>-22.14073946380772</v>
+        <v>-21.54043136392891</v>
       </c>
       <c r="F87">
-        <v>-1.541571174672318</v>
+        <v>-1.487072054874735</v>
       </c>
       <c r="G87">
-        <v>-5.476600486525546</v>
+        <v>-5.475586589063677</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.299533081993402</v>
       </c>
       <c r="E88">
-        <v>-21.76362626234496</v>
+        <v>-23.05976609282038</v>
       </c>
       <c r="F88">
-        <v>-1.522059808866778</v>
+        <v>-1.516203251328986</v>
       </c>
       <c r="G88">
-        <v>-5.730895157382511</v>
+        <v>-5.129968959764247</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.01765277239626841</v>
       </c>
       <c r="E89">
-        <v>-23.21082240029423</v>
+        <v>-22.15052096766429</v>
       </c>
       <c r="F89">
-        <v>-1.537349814387651</v>
+        <v>-1.209508504116497</v>
       </c>
       <c r="G89">
-        <v>-5.093065060885172</v>
+        <v>-3.992766472913456</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.2284116166516497</v>
       </c>
       <c r="E90">
-        <v>-24.80149418022852</v>
+        <v>-25.60653458999411</v>
       </c>
       <c r="F90">
-        <v>-2.155515675257171</v>
+        <v>-1.233764758405272</v>
       </c>
       <c r="G90">
-        <v>-5.292369739627403</v>
+        <v>-3.743600351353903</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.4320612620469035</v>
       </c>
       <c r="E91">
-        <v>-26.42945341514197</v>
+        <v>-25.53289254568137</v>
       </c>
       <c r="F91">
-        <v>-2.017854266790338</v>
+        <v>-1.619747519944118</v>
       </c>
       <c r="G91">
-        <v>-5.283982937321462</v>
+        <v>-2.806926438887017</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.5901557820745402</v>
       </c>
       <c r="E92">
-        <v>-28.17732211330452</v>
+        <v>-28.97147607155566</v>
       </c>
       <c r="F92">
-        <v>-2.162896428816115</v>
+        <v>-2.048860058677124</v>
       </c>
       <c r="G92">
-        <v>-5.122274495207348</v>
+        <v>-2.59063487613154</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.7015962639316194</v>
       </c>
       <c r="E93">
-        <v>-29.00493243752434</v>
+        <v>-29.32644050664691</v>
       </c>
       <c r="F93">
-        <v>-2.168512759807096</v>
+        <v>-2.206094960504706</v>
       </c>
       <c r="G93">
-        <v>-4.731763192531595</v>
+        <v>-3.360429141306627</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.7633854590006869</v>
       </c>
       <c r="E94">
-        <v>-30.70369662778471</v>
+        <v>-31.72801707018671</v>
       </c>
       <c r="F94">
-        <v>-2.459557990045896</v>
+        <v>-2.98642865108548</v>
       </c>
       <c r="G94">
-        <v>-5.535642787266194</v>
+        <v>-4.619364948012816</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.7767241089229171</v>
       </c>
       <c r="E95">
-        <v>-33.51260716407746</v>
+        <v>-33.24596608603182</v>
       </c>
       <c r="F95">
-        <v>-2.764471747342366</v>
+        <v>-2.854938579769503</v>
       </c>
       <c r="G95">
-        <v>-5.381474592295683</v>
+        <v>-5.055806790077677</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.7424992876615464</v>
       </c>
       <c r="E96">
-        <v>-34.44039639029496</v>
+        <v>-34.46835971729232</v>
       </c>
       <c r="F96">
-        <v>-2.742398241159968</v>
+        <v>-2.605672059490896</v>
       </c>
       <c r="G96">
-        <v>-5.672555038055584</v>
+        <v>-5.127770541319419</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.666835382302052</v>
       </c>
       <c r="E97">
-        <v>-36.16212900072224</v>
+        <v>-36.91399154021575</v>
       </c>
       <c r="F97">
-        <v>-2.811503135003711</v>
+        <v>-2.904424420045343</v>
       </c>
       <c r="G97">
-        <v>-5.586498440216027</v>
+        <v>-4.748070863682035</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.5498554223233524</v>
       </c>
       <c r="E98">
-        <v>-39.37363672595591</v>
+        <v>-37.68805945200587</v>
       </c>
       <c r="F98">
-        <v>-2.642796173014758</v>
+        <v>-3.365147458869177</v>
       </c>
       <c r="G98">
-        <v>-7.050490907058155</v>
+        <v>-5.366951905673582</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.4082494672302554</v>
       </c>
       <c r="E99">
-        <v>-41.38798121286282</v>
+        <v>-40.62751230851773</v>
       </c>
       <c r="F99">
-        <v>-2.51440088231564</v>
+        <v>-3.666626804913641</v>
       </c>
       <c r="G99">
-        <v>-6.51090058405059</v>
+        <v>-5.883452272567333</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.2354631234485431</v>
       </c>
       <c r="E100">
-        <v>-42.29624365915924</v>
+        <v>-42.5533319212857</v>
       </c>
       <c r="F100">
-        <v>-3.025753736798581</v>
+        <v>-3.029863267483869</v>
       </c>
       <c r="G100">
-        <v>-6.990674238029477</v>
+        <v>-6.380951085410342</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.06290868647149832</v>
       </c>
       <c r="E101">
-        <v>-44.92913241077384</v>
+        <v>-44.56087237599608</v>
       </c>
       <c r="F101">
-        <v>-3.002143609083989</v>
+        <v>-3.294819894738902</v>
       </c>
       <c r="G101">
-        <v>-7.17325124926166</v>
+        <v>-6.124398934120478</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.1410049670681065</v>
       </c>
       <c r="E102">
-        <v>-45.81902057378414</v>
+        <v>-46.8116688689765</v>
       </c>
       <c r="F102">
-        <v>-2.832164274764336</v>
+        <v>-3.279086712657531</v>
       </c>
       <c r="G102">
-        <v>-7.6568475263573</v>
+        <v>-6.573115826039222</v>
       </c>
     </row>
   </sheetData>
